--- a/documents/marketing.xlsx
+++ b/documents/marketing.xlsx
@@ -516,7 +516,6 @@
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>137300</v>
       </c>
@@ -568,7 +567,6 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>104400</v>
       </c>
@@ -620,7 +618,6 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>86900</v>
       </c>
@@ -672,7 +669,6 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>108000</v>
       </c>
@@ -724,7 +720,6 @@
           <t>2022-01-03</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>83900</v>
       </c>
@@ -776,7 +771,6 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>72100</v>
       </c>
@@ -828,7 +822,6 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>74000</v>
       </c>
@@ -880,7 +873,6 @@
           <t>2019-12-01</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
         <v>81100</v>
       </c>
@@ -932,7 +924,6 @@
           <t>2025-11-12</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>79500</v>
       </c>
@@ -984,7 +975,6 @@
           <t>2021-03-05</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>97600</v>
       </c>
@@ -1036,7 +1026,6 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>107400</v>
       </c>
@@ -1088,7 +1077,6 @@
           <t>2021-02-26</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
         <v>95500</v>
       </c>
@@ -1140,7 +1128,6 @@
           <t>2020-09-12</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
         <v>94800</v>
       </c>
@@ -1192,7 +1179,6 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
         <v>82400</v>
       </c>
@@ -1244,7 +1230,6 @@
           <t>2021-08-09</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
         <v>93300</v>
       </c>
@@ -1296,7 +1281,6 @@
           <t>2022-07-12</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
         <v>90300</v>
       </c>
@@ -1348,7 +1332,6 @@
           <t>2022-04-23</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
         <v>83900</v>
       </c>
@@ -1400,7 +1383,6 @@
           <t>2019-03-20</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
         <v>96300</v>
       </c>
@@ -1452,7 +1434,6 @@
           <t>2026-02-23</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
         <v>79700</v>
       </c>
@@ -1504,7 +1485,6 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>120900</v>
       </c>
@@ -1556,7 +1536,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
         <v>126300</v>
       </c>
@@ -1608,7 +1587,6 @@
           <t>2018-07-23</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
         <v>84000</v>
       </c>
@@ -1660,7 +1638,6 @@
           <t>2022-05-04</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
         <v>92300</v>
       </c>
@@ -1712,7 +1689,6 @@
           <t>2019-01-21</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
         <v>85300</v>
       </c>
@@ -1764,7 +1740,6 @@
           <t>2018-11-23</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
         <v>138300</v>
       </c>
@@ -1816,7 +1791,6 @@
           <t>2023-02-28</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
         <v>130700</v>
       </c>
@@ -1868,7 +1842,6 @@
           <t>2018-04-03</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
         <v>132500</v>
       </c>
@@ -1920,7 +1893,6 @@
           <t>2024-01-09</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
         <v>105500</v>
       </c>
@@ -1972,7 +1944,6 @@
           <t>2024-08-15</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
         <v>86000</v>
       </c>
@@ -2024,7 +1995,6 @@
           <t>2024-10-11</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
         <v>79100</v>
       </c>
@@ -2076,7 +2046,6 @@
           <t>2023-11-13</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
         <v>85200</v>
       </c>
@@ -2128,7 +2097,6 @@
           <t>2021-01-04</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
         <v>122200</v>
       </c>
@@ -2180,7 +2148,6 @@
           <t>2023-01-06</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
         <v>88500</v>
       </c>
@@ -2232,7 +2199,6 @@
           <t>2022-04-07</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
         <v>74900</v>
       </c>
@@ -2284,7 +2250,6 @@
           <t>2023-07-04</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
         <v>72600</v>
       </c>
@@ -2336,7 +2301,6 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
         <v>69000</v>
       </c>
@@ -2388,7 +2352,6 @@
           <t>2021-07-19</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
         <v>140100</v>
       </c>
@@ -2440,7 +2403,6 @@
           <t>2022-05-22</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
         <v>79200</v>
       </c>
@@ -2492,7 +2454,6 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
         <v>111900</v>
       </c>
@@ -2544,7 +2505,6 @@
           <t>2024-04-25</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
         <v>127800</v>
       </c>
@@ -2596,7 +2556,6 @@
           <t>2022-10-21</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
         <v>79200</v>
       </c>
@@ -2648,7 +2607,6 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
         <v>88200</v>
       </c>
@@ -2700,7 +2658,6 @@
           <t>2024-12-16</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
         <v>88800</v>
       </c>
@@ -2752,7 +2709,6 @@
           <t>2024-04-15</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
         <v>127000</v>
       </c>
@@ -2804,7 +2760,6 @@
           <t>2021-01-02</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
         <v>94900</v>
       </c>
@@ -2856,7 +2811,6 @@
           <t>2023-07-11</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
         <v>72000</v>
       </c>
@@ -2908,7 +2862,6 @@
           <t>2022-05-28</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
         <v>89700</v>
       </c>
@@ -2960,7 +2913,6 @@
           <t>2021-12-12</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
         <v>86300</v>
       </c>
@@ -3012,7 +2964,6 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
         <v>79200</v>
       </c>
@@ -3064,7 +3015,6 @@
           <t>2024-03-10</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
         <v>78300</v>
       </c>
@@ -3116,7 +3066,6 @@
           <t>2022-10-24</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
         <v>80700</v>
       </c>
@@ -3168,7 +3117,6 @@
           <t>2023-06-17</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
         <v>84100</v>
       </c>
@@ -3220,7 +3168,6 @@
           <t>2024-12-13</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
         <v>87000</v>
       </c>
@@ -3272,7 +3219,6 @@
           <t>2024-09-09</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
         <v>126800</v>
       </c>
@@ -3324,7 +3270,6 @@
           <t>2019-07-28</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
         <v>112200</v>
       </c>
@@ -3376,7 +3321,6 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
         <v>113600</v>
       </c>
@@ -3428,7 +3372,6 @@
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
         <v>107300</v>
       </c>
@@ -3480,7 +3423,6 @@
           <t>2019-05-27</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
         <v>110800</v>
       </c>
@@ -3532,7 +3474,6 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
         <v>100400</v>
       </c>
@@ -3584,7 +3525,6 @@
           <t>2018-05-18</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
         <v>133800</v>
       </c>
@@ -3636,7 +3576,6 @@
           <t>2022-04-15</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
         <v>129200</v>
       </c>
@@ -3688,7 +3627,6 @@
           <t>2020-04-13</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
         <v>104400</v>
       </c>
@@ -3740,7 +3678,6 @@
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
         <v>103900</v>
       </c>
@@ -3792,7 +3729,6 @@
           <t>2023-06-05</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
         <v>85200</v>
       </c>
@@ -3844,7 +3780,6 @@
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
         <v>72100</v>
       </c>
@@ -3896,7 +3831,6 @@
           <t>2026-02-17</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
         <v>109500</v>
       </c>
@@ -3948,7 +3882,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
         <v>80200</v>
       </c>
@@ -4000,7 +3933,6 @@
           <t>2024-01-15</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
         <v>82900</v>
       </c>
@@ -4052,7 +3984,6 @@
           <t>2023-02-19</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
         <v>144400</v>
       </c>
@@ -4104,7 +4035,6 @@
           <t>2022-11-06</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
         <v>91900</v>
       </c>
@@ -4156,7 +4086,6 @@
           <t>2020-12-09</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
         <v>92000</v>
       </c>
@@ -4208,7 +4137,6 @@
           <t>2021-03-15</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
         <v>121600</v>
       </c>
@@ -4260,7 +4188,6 @@
           <t>2023-03-20</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
         <v>113400</v>
       </c>
@@ -4312,7 +4239,6 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
         <v>113400</v>
       </c>
@@ -4364,7 +4290,6 @@
           <t>2025-05-26</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
         <v>86900</v>
       </c>
@@ -4416,7 +4341,6 @@
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
         <v>113900</v>
       </c>
@@ -4468,7 +4392,6 @@
           <t>2024-02-13</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
         <v>75400</v>
       </c>
@@ -4520,7 +4443,6 @@
           <t>2024-05-17</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
         <v>86500</v>
       </c>
@@ -4572,7 +4494,6 @@
           <t>2021-08-04</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
         <v>80500</v>
       </c>
@@ -4624,7 +4545,6 @@
           <t>2025-06-20</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
         <v>95900</v>
       </c>
@@ -4676,7 +4596,6 @@
           <t>2018-01-09</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
         <v>134300</v>
       </c>
@@ -4728,7 +4647,6 @@
           <t>2023-09-08</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
         <v>141300</v>
       </c>
@@ -4780,7 +4698,6 @@
           <t>2023-10-21</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
         <v>110000</v>
       </c>
@@ -4832,7 +4749,6 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
         <v>68300</v>
       </c>
@@ -4884,7 +4800,6 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
         <v>85300</v>
       </c>
@@ -4936,7 +4851,6 @@
           <t>2022-05-19</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
         <v>109700</v>
       </c>
@@ -4988,7 +4902,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
         <v>102000</v>
       </c>
@@ -5040,7 +4953,6 @@
           <t>2022-05-05</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
         <v>131700</v>
       </c>
@@ -5092,7 +5004,6 @@
           <t>2024-04-02</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
         <v>84500</v>
       </c>
@@ -5144,7 +5055,6 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
         <v>72100</v>
       </c>
@@ -5196,7 +5106,6 @@
           <t>2022-11-10</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
         <v>87400</v>
       </c>
@@ -5248,7 +5157,6 @@
           <t>2023-09-16</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
         <v>113700</v>
       </c>
@@ -5300,7 +5208,6 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
         <v>107600</v>
       </c>
@@ -5352,7 +5259,6 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
         <v>94100</v>
       </c>
@@ -5404,7 +5310,6 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
         <v>127500</v>
       </c>
@@ -5456,7 +5361,6 @@
           <t>2023-02-23</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
         <v>77600</v>
       </c>
@@ -5508,7 +5412,6 @@
           <t>2023-12-11</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
         <v>103600</v>
       </c>
@@ -5560,7 +5463,6 @@
           <t>2022-11-15</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
         <v>126400</v>
       </c>
@@ -5612,7 +5514,6 @@
           <t>2020-08-12</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
         <v>79000</v>
       </c>
@@ -5664,7 +5565,6 @@
           <t>2023-09-17</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
         <v>77600</v>
       </c>
@@ -5716,7 +5616,6 @@
           <t>2025-07-19</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
         <v>88500</v>
       </c>
@@ -5768,7 +5667,6 @@
           <t>2023-12-11</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
         <v>112800</v>
       </c>
@@ -5820,7 +5718,6 @@
           <t>2022-04-09</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
         <v>92700</v>
       </c>
@@ -5872,7 +5769,6 @@
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
         <v>107800</v>
       </c>
@@ -5924,7 +5820,6 @@
           <t>2021-02-20</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="n">
         <v>105200</v>
       </c>
@@ -5976,7 +5871,6 @@
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
         <v>130300</v>
       </c>
@@ -6028,7 +5922,6 @@
           <t>2022-02-09</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
         <v>134100</v>
       </c>
@@ -6080,7 +5973,6 @@
           <t>2022-06-21</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
       <c r="G109" t="n">
         <v>87500</v>
       </c>
@@ -6132,7 +6024,6 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
         <v>84000</v>
       </c>
@@ -6184,7 +6075,6 @@
           <t>2022-05-27</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
         <v>95600</v>
       </c>
@@ -6236,7 +6126,6 @@
           <t>2021-02-18</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
         <v>86200</v>
       </c>
@@ -6288,7 +6177,6 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="n">
         <v>106900</v>
       </c>
@@ -6340,7 +6228,6 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="n">
         <v>142400</v>
       </c>
@@ -6458,7 +6345,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -7018,7 +6905,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I126" t="n">
@@ -7074,7 +6961,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I127" t="n">
@@ -7344,7 +7231,6 @@
           <t>2022-11-23</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
       <c r="G132" t="n">
         <v>97800</v>
       </c>
@@ -7406,7 +7292,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I133" t="n">
@@ -7462,7 +7348,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I134" t="n">
@@ -7518,7 +7404,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I135" t="n">
@@ -7630,7 +7516,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I137" t="n">
@@ -7844,7 +7730,6 @@
           <t>2024-05-11</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
       <c r="G141" t="n">
         <v>80500</v>
       </c>
@@ -7962,7 +7847,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I143" t="n">
@@ -8018,7 +7903,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I144" t="n">
@@ -8074,7 +7959,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I145" t="n">
@@ -8130,7 +8015,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I146" t="n">
@@ -8344,7 +8229,6 @@
           <t>2024-04-22</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
         <v>109300</v>
       </c>
@@ -8462,7 +8346,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -8574,7 +8458,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I154" t="n">
@@ -8854,7 +8738,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I159" t="n">
@@ -9012,7 +8896,6 @@
           <t>2024-10-21</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
         <v>130300</v>
       </c>
@@ -9298,7 +9181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I167" t="n">
@@ -9344,7 +9227,6 @@
           <t>2023-10-01</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr"/>
       <c r="G168" t="n">
         <v>99900</v>
       </c>
@@ -9732,7 +9614,6 @@
           <t>2024-03-15</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr"/>
       <c r="G175" t="n">
         <v>105500</v>
       </c>
@@ -9794,7 +9675,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I176" t="n">
@@ -9906,7 +9787,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I178" t="n">
@@ -9952,7 +9833,6 @@
           <t>2021-12-15</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
         <v>86400</v>
       </c>
@@ -10014,7 +9894,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I180" t="n">
@@ -10228,7 +10108,6 @@
           <t>2024-02-24</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr"/>
       <c r="G184" t="n">
         <v>95400</v>
       </c>
@@ -10448,7 +10327,6 @@
           <t>2020-06-15</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
         <v>96000</v>
       </c>
@@ -10556,7 +10434,6 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr"/>
       <c r="G190" t="n">
         <v>102900</v>
       </c>
@@ -10608,7 +10485,6 @@
           <t>2024-01-05</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr"/>
       <c r="G191" t="n">
         <v>72400</v>
       </c>
@@ -10660,7 +10536,6 @@
           <t>2024-07-06</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr"/>
       <c r="G192" t="n">
         <v>98400</v>
       </c>
@@ -10768,7 +10643,6 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr"/>
       <c r="G194" t="n">
         <v>93100</v>
       </c>
@@ -10830,7 +10704,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I195" t="n">
@@ -11054,7 +10928,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I199" t="n">
@@ -11110,7 +10984,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I200" t="n">
@@ -11166,7 +11040,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I201" t="n">
@@ -11446,7 +11320,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I206" t="n">
@@ -11670,7 +11544,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I210" t="n">
@@ -12342,7 +12216,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I222" t="n">
@@ -12566,7 +12440,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I226" t="n">
@@ -12678,7 +12552,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I228" t="n">
@@ -12734,7 +12608,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I229" t="n">
@@ -13014,7 +12888,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I234" t="n">
@@ -13126,7 +13000,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I236" t="n">
@@ -13182,7 +13056,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I237" t="n">
@@ -13350,7 +13224,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I240" t="n">
@@ -13396,7 +13270,6 @@
           <t>2024-07-02</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
         <v>94200</v>
       </c>
@@ -13626,7 +13499,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I245" t="n">
@@ -13794,7 +13667,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I248" t="n">
@@ -13962,7 +13835,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I251" t="n">
@@ -14074,7 +13947,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I253" t="n">
@@ -14186,7 +14059,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I255" t="n">

--- a/documents/marketing.xlsx
+++ b/documents/marketing.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L261"/>
+  <dimension ref="A1:L271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,12 +873,17 @@
           <t>2019-12-01</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
       <c r="G9" t="n">
         <v>81100</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1128,12 +1133,17 @@
           <t>2020-09-12</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
       <c r="G14" t="n">
         <v>94800</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1332,12 +1342,17 @@
           <t>2022-04-23</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="G18" t="n">
         <v>83900</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1485,12 +1500,17 @@
           <t>2022-04-01</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
       <c r="G21" t="n">
         <v>120900</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1740,12 +1760,17 @@
           <t>2018-11-23</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
       <c r="G26" t="n">
         <v>138300</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1842,12 +1867,17 @@
           <t>2018-04-03</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="G28" t="n">
         <v>132500</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2454,12 +2484,17 @@
           <t>2022-10-13</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
       <c r="G40" t="n">
         <v>111900</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -3015,12 +3050,17 @@
           <t>2024-03-10</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="G51" t="n">
         <v>78300</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -3066,12 +3106,17 @@
           <t>2022-10-24</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
       <c r="G52" t="n">
         <v>80700</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -3678,12 +3723,17 @@
           <t>2021-07-01</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="G64" t="n">
         <v>103900</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -3933,12 +3983,17 @@
           <t>2024-01-15</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="G69" t="n">
         <v>82900</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4086,12 +4141,17 @@
           <t>2020-12-09</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
       <c r="G72" t="n">
         <v>92000</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -4290,12 +4350,17 @@
           <t>2025-05-26</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
       <c r="G76" t="n">
         <v>86900</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -4392,12 +4457,17 @@
           <t>2024-02-13</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="G78" t="n">
         <v>75400</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -4749,12 +4819,17 @@
           <t>2021-10-13</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="G85" t="n">
         <v>68300</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -4902,12 +4977,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="G88" t="n">
         <v>102000</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -5361,12 +5441,17 @@
           <t>2023-02-23</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
       <c r="G97" t="n">
         <v>77600</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I97" t="n">
@@ -5412,12 +5497,17 @@
           <t>2023-12-11</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
       <c r="G98" t="n">
         <v>103600</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I98" t="n">
@@ -5616,12 +5706,17 @@
           <t>2025-07-19</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="G102" t="n">
         <v>88500</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -5718,12 +5813,17 @@
           <t>2022-04-09</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="G104" t="n">
         <v>92700</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -6177,12 +6277,17 @@
           <t>2022-08-19</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
       <c r="G113" t="n">
         <v>106900</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I113" t="n">
@@ -14410,6 +14515,516 @@
         </is>
       </c>
       <c r="L261" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Jeffrey Harris</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>1993-02-07</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Digital Marketing Manager</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>124100</v>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I262" t="n">
+        <v>2</v>
+      </c>
+      <c r="J262" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Anthony Green</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>1987-09-19</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>75100</v>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I263" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Sandra Carter</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>1990-12-19</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Digital Marketing Manager</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>116600</v>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I264" t="n">
+        <v>2</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Hispanic</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Madison Hall</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>1986-09-21</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>90300</v>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I265" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Sandra Roberts</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>1983-08-27</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Content Strategist</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>103300</v>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I266" t="n">
+        <v>3</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Kathleen Hall</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2000-07-04</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Digital Marketing Manager</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>107400</v>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I267" t="n">
+        <v>3</v>
+      </c>
+      <c r="J267" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Melissa Scott</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>1981-04-21</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>91300</v>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I268" t="n">
+        <v>3</v>
+      </c>
+      <c r="J268" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>John King</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>1997-02-13</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>82900</v>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I269" t="n">
+        <v>3</v>
+      </c>
+      <c r="J269" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Melissa Cook</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>1980-09-02</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>92600</v>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I270" t="n">
+        <v>3</v>
+      </c>
+      <c r="J270" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Steven Martin</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2004-03-11</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Marketing Coordinator</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>68600</v>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I271" t="n">
+        <v>2</v>
+      </c>
+      <c r="J271" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
         <is>
           <t>White</t>
         </is>
